--- a/crates/unluminous-sheet/_agent_output/pivot/explore/exp1/edge_text_fn.xlsx
+++ b/crates/unluminous-sheet/_agent_output/pivot/explore/exp1/edge_text_fn.xlsx
@@ -699,7 +699,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Val" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsMixedTypes="1" containsNumber="1" minValue="-10" maxValue="20" count="10">
+      <sharedItems containsString="0" containsMixedTypes="1" containsNumber="1" minValue="-10" maxValue="20" count="10">
         <n v="10"/>
         <n v="-10"/>
         <n v="0"/>
@@ -859,6 +859,11 @@
     <dataField name="Product of Group2" fld="0" subtotal="product" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
 </pivotTableDefinition>
 </file>
 
